--- a/AAII_Financials/Quarterly/CRZBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRZBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="92">
   <si>
     <t>CRZBY</t>
   </si>
@@ -656,149 +656,152 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -841,86 +844,89 @@
       <c r="P8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3">
         <v>4009500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2720100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2403600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2161000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2075000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1869500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1864200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1963600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1753400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1897300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2068400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2294200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2458600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8165800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2630400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2648400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2636700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2437800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2333300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2267400</v>
-      </c>
-      <c r="AK8" s="3">
-        <v>2304600</v>
       </c>
       <c r="AL8" s="3">
         <v>2304600</v>
       </c>
       <c r="AM8" s="3">
+        <v>2304600</v>
+      </c>
+      <c r="AN8" s="3">
         <v>2348300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2508400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1556500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1339300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,8 +1047,11 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1495,8 +1514,8 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1573,8 +1592,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1617,14 +1639,14 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>5</v>
@@ -1641,62 +1663,65 @@
       <c r="X15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-239400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-243900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-261800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-254200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-295400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-917500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-292900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-299100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-195200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-179400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-181200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-183400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-209800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-172800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-167200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-163200</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-159600</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-140900</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,8 +1761,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1780,86 +1806,89 @@
       <c r="P17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>2086700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1058000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>910700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1141400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1005000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>684900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>714200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>794600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1284700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>906100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1188000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1208700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1225800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4008200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1339900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1269200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1048000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1229400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1118900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1146300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1235300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1328400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1409200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1506000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1493100</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>322800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1902,86 +1931,89 @@
       <c r="P18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>1922800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1662100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1492900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1019500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1070000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1184600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1150000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1169100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>468800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>991200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>880400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1085500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1232800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4157600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1290500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1379200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1588600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1208400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1214400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1121100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1069300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>976100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>939100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1002400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>63400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1016500</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,86 +2101,89 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1380100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1373600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-708400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-443900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-944300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-758100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1656800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1091900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2983200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1024400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-658900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1387600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1091500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2927700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-924700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1087300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1322500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-825200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-774100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-837800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1046800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-277100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1648200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-615100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>294600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-1315800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2214,62 +2250,65 @@
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-2275100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-39400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>230200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-318500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-443600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2147400</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="3">
         <v>379900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>438100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>466700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>219900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>871800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-697900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>550500</v>
       </c>
-      <c r="AO21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AP21" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,8 +2429,11 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2434,86 +2476,89 @@
       <c r="P23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>542700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>288500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>784500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>575600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>125800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>426500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-506800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>77200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2514400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-33200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>221500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-302200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>141300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1229900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>365900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>291900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>266200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>383200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>440300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>283300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>22400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>699000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-709100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>387400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>358000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-299300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2556,86 +2601,89 @@
       <c r="P24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>-45400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>246400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>245900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>216500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-215700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-6500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>42300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-87800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>203500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>8700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>58900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>206600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>298900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>29400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>116000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>95800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>103000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>108700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-7700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>14600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>151500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-15700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>95100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>117400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,8 +2804,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2800,86 +2851,89 @@
       <c r="P26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>588100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>42100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>538600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>359100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>341500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>432900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-549100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>165000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2717900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-36300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>212700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-361100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-65400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>931000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>336500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>175800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>170300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>280200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>331600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>291000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>7900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>547500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-693400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>292300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>240600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-315800</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2922,86 +2976,89 @@
       <c r="P27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>522800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>210700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>304700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>324300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>457500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>432900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-704600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>140700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2691000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-51900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>198500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-369800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-80600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>822000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>302300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>159100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>146700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>252500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>305200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>254700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-23600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>524000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-721400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>268800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>214800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-338100</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3166,20 +3226,20 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -3191,52 +3251,52 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>6500</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>48000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-31500</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>11000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>29400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-15600</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-11800</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-11100</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-7700</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>32900</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>107700</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
+      <c r="AN29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AO29" s="3">
         <v>0</v>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,86 +3601,89 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>1380100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1373600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>708400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>443900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>944300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>758100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1656800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1091900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2983200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1024400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>658900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1387600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1091500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2927700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>924700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1087300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1322500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>825200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>774100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>837800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1046800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>277100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1648200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>615100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-294600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>1315800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3654,86 +3726,89 @@
       <c r="P33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>522800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>210700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>304700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>324300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>457500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>432900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-704600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>140700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2701000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-61200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>205100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-321800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-112100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>833000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>331700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>143500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>134900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>241500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>297600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>287700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>84100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>524000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-721400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>268800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>214800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-338100</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,8 +3929,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3898,213 +3976,219 @@
       <c r="P35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>522800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>210700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>304700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>324300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>457500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>432900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-704600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>140700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2701000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-61200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>205100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-321800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-112100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>833000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>331700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>143500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>134900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>241500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>297600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>287700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>84100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>524000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-721400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>268800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>214800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-338100</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,297 +4276,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>67359800</v>
+      </c>
+      <c r="E41" s="3">
         <v>75481400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>37014200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>81271900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>85100400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>83256600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>47509100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>106212400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>111531100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>117686900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>72754500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>92664100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>92750000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>95188000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>204035400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>127147600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>113941500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>108281200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>74196900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>111192100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>133415900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>99307100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>98151100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>116233400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>120571700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>98273500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>77583700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>109365900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>118794000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>117233600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>101498700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>107143700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>105166400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>97220200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>62531900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>86884700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>92703300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>84554200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>72001500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>60858500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>49901700</v>
+      </c>
+      <c r="E42" s="3">
         <v>40311300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>130983900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>37632300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>38344100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>31713100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>103158700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>31577100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>30889300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>25863600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>79102500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>27704300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>72248900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>27879200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>147588800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>119177400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>125215300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>122556000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>117143500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>140355600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>138322900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>139868700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>127013900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>147841600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>157636500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>145161900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>127164800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>166353600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>149408700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>142506900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>124073200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>157879500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>153503700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>147111100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>99888500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>125609000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>129316100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>143882100</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>175673600</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>178166800</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>181700</v>
+      </c>
+      <c r="E43" s="3">
         <v>403600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>374500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>525600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>409900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>324300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>223600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>172900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>170400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>176900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>152500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>137600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>182300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>178200</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4557,8 +4649,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>956200</v>
+      </c>
+      <c r="E45" s="3">
         <v>4681200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>806600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3720500</v>
       </c>
-      <c r="G45" s="3">
-        <v>886700</v>
-      </c>
       <c r="H45" s="3">
+        <v>544900</v>
+      </c>
+      <c r="I45" s="3">
         <v>2479500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>547700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3689500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>595700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3006800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>487500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3650500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>260900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2596700</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>118606200</v>
+      </c>
+      <c r="E46" s="3">
         <v>120877400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>203117300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>123150300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>124953600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>117773500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>179508200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>141651800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>143186500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>146734300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>182678200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>124156400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>165800200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>125842000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,374 +5024,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>128176600</v>
+      </c>
+      <c r="E47" s="3">
         <v>532272600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>131036800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>532550700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>125607800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>464559000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>96705700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>456952900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>86752400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>419401200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>81987400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>394193500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>76430100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>392768400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>201600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>198800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>192600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>191500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>189700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>186300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>179900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>180900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>168600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>184700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>196400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>198500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>206600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>221700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>209400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>217700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>204600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>200500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>187800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>175700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>203100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>365800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>360200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>386200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>389700</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1021200</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2316900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2381000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2457400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2517900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2520300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2389800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2323200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2489400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2446200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2509400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2599800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2448100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2526200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2613000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5437200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2846600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2994500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3079300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3167700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3265200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3235400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3323200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6412300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3240300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3579300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3663300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4085900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4414900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4300900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4534800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1845300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1701300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1666800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1728300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1813100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1798500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1842300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2007200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>4063700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2021300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2194700</v>
+      </c>
+      <c r="E49" s="3">
         <v>2155000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2182700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2149500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2106900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1956300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1848000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1927300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1806500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1537400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1540800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1424600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1476000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1417900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2855400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1363800</v>
-      </c>
-      <c r="S49" s="3">
-        <v>1364500</v>
       </c>
       <c r="T49" s="3">
         <v>1364500</v>
       </c>
       <c r="U49" s="3">
+        <v>1364500</v>
+      </c>
+      <c r="V49" s="3">
         <v>1347500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1303000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1281200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1479100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2832600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3049400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3248700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3257500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3564100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3799900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3695100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3813500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3839700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3606300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3588300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3612400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3694700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3574700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3506200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>3588300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>4073100</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>3473300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3522200</v>
+      </c>
+      <c r="E52" s="3">
         <v>36213500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3727800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>33646600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3195500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31578000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2807700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25315600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2685100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22878400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2546700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14886700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2370100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14563200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4313000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3821400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4641800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4344800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4850300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4378700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5233900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5052000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4815400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5180200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5484000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8535300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>12690900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>15306300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>20332900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>21269600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>19569900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3781300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>3809000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>3683800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3419800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>3661100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>4798800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>5379600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>4957000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>4757500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>707254700</v>
+      </c>
+      <c r="E54" s="3">
         <v>695604800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>692840200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>695706900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>683286000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>620047600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>574227100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>630528700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>600114600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>595508700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>571643600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>539675100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>547601500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>540370500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>528799300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>587217800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>582186800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>571895600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>506718100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>582880700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>575174300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>568996600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>505295800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>564960100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>600685600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>564295000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>541036200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>628840000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>609410500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>601982900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>546956400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>546292700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>535315600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>516095100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>507694900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>549668500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>546700800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>575468600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>563940600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>602685700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,52 +6116,53 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3">
+        <v>538777600</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3">
         <v>537913600</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3">
         <v>520448600</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3">
         <v>449018500</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>481810800</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3">
         <v>453375700</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3">
         <v>433372300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -6091,8 +6221,8 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
-      <c r="AK57" s="3" t="s">
-        <v>5</v>
+      <c r="AK57" s="3">
+        <v>0</v>
       </c>
       <c r="AL57" s="3" t="s">
         <v>5</v>
@@ -6109,53 +6239,56 @@
       <c r="AP57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>46491500</v>
+      </c>
+      <c r="E58" s="3">
         <v>23607700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>35032300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19377000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>40853800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18473800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>24064600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20904500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16153400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17665300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20013300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>21561200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>17104800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>21515600</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6231,175 +6364,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3745000</v>
+      </c>
+      <c r="E59" s="3">
         <v>904000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3117300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>860000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3119200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>452900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2068500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>567700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3800500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>577200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2842900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>598000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3500000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>939800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1313600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>630000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>915100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>600600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>890000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>599800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>973400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>405200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>719100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>639300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>773500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>817100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>868600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>885700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>827000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>909100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>927400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>892700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>947600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>926700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1062500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>935700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>969400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1121000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1166800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>932000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>589732700</v>
+      </c>
+      <c r="E60" s="3">
         <v>24511700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>576800500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20237000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>564421600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18926700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>475634100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21472200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>502283300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18242500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>477563800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22159200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>453977100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22455500</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,252 +6614,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>69874300</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>67172700</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>69347000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>55272800</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>54408000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>51760800</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>52108100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>48474100</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>45724100</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>47532400</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>45475000</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>46003100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>49211000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>52902600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>52315700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>52855700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>56430400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>59963500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>60217900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>54874700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>53373000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>48676500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>47827800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>48659600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>53590700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>52791900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>56584700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>54887400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>62618100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6448100</v>
+      </c>
+      <c r="E62" s="3">
         <v>629955000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6686600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>633470600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6763400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>561851500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5655900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>570193000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6931300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>541423000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5104500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>482920200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5990200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>483396300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7713300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4277400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4311100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4836600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4873000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5607400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6163900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5975600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8277400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5477000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6349100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8005100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>13107700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>16957500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>19164700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>19516000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>19035200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3929800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4138400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3774900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3723900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>4178300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>4220900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>4241000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>4090700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>4472200</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>666771400</v>
+      </c>
+      <c r="E66" s="3">
         <v>654476000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>651318500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>653736900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>641914300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>580818200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>537249200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>591715400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>564335200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>559669900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>535158600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>505084700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>512728200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>505858300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>495520300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>555090700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>550065000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>540414700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>475439600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>552013600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>545423300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>539161000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>477912200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>533045700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>567395400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>532379400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>506943100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>592799600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>576267800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>568277500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>513579700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>514859000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>504562800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>485487300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>475316500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>517553800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>514984400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>541750900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>530431800</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>569398800</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22031300</v>
+      </c>
+      <c r="E72" s="3">
         <v>22760300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>22632400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22747900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>22246600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>21027900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19664600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20902300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19382800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19589000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19924800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18993400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>29786000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18712500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18269900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17410100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17351900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>16678400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>16239800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14292600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13445100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14083000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12543300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10507700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11258200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11496000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11726600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12568400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11671100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>32468500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>32236400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>30294000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>29676700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>29435200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>31889200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>31856700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>31373100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>33371400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>33230600</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>33059200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38577600</v>
+      </c>
+      <c r="E76" s="3">
         <v>39303600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>39719400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>40261600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>39734600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>37794000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>35684900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>37489400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>34576200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>34714600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>35362000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>33558400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>33810000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>33502800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>33278900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>32127000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>32121800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>31480900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>31278500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>30867200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>29751000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>29835600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>27383600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>31914400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>33290200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>31915700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>34093000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>36040400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>33142700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>33705300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>33376700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>31433700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>30752800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>30607800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>32378400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>32114700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>31716400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>33717700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>33508800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>33286900</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,135 +8659,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8642,86 +8836,89 @@
       <c r="P81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>522800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>210700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>304700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>324300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>457500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>432900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-704600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>140700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2701000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-61200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>205100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-321800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-112100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>833000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>331700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>143500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>134900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>241500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>297600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>287700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>84100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>524000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-721400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>268800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>214800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-338100</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,8 +8961,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8808,8 +9006,8 @@
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8886,8 +9084,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,8 +9709,11 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9540,8 +9756,8 @@
       <c r="P89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
@@ -9555,8 +9771,8 @@
       <c r="U89" s="3">
         <v>0</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
@@ -9564,62 +9780,65 @@
       <c r="X89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>33588400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>358100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>28712800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>27820400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-13505800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>957900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>5699700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>9435600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-3745100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1664700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2732900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1348300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-862800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>23787300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>8684200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>14763000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>20068600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>8435000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9784,8 +10004,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,8 +10254,11 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -10072,8 +10301,8 @@
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -10087,8 +10316,8 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
@@ -10096,62 +10325,65 @@
       <c r="X94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-1217800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-79900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-197500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>881500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-793800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-200900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-29400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-185400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-307600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-273600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>51600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-105400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-13134000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>12624600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>5677300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>5440600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>6558100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>5123700</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,8 +10471,8 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10316,8 +10549,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,8 +10924,11 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10726,8 +10971,8 @@
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -10741,8 +10986,8 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
@@ -10750,62 +10995,65 @@
       <c r="X100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>2202300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-323800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2298500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1112700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2870700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1570400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>197600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>33500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>207000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>329000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>206400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-364500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>85300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-391600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-310800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-31700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1277100</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>1025900</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10863,8 +11111,8 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
@@ -10872,62 +11120,65 @@
       <c r="X101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-222400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-126600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>15300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-175600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-17500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>89400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>81300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>23700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>56500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>170200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-130700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>58300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-205300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-158200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>64600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>234800</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10967,8 +11218,8 @@
       <c r="O102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
@@ -10985,8 +11236,8 @@
       <c r="U102" s="3">
         <v>0</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
@@ -10994,58 +11245,61 @@
       <c r="X102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>34350500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-172300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>30829100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>29638900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-13838500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1097600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>5224400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>7886500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-5324200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1838600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3144700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2022500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1100700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>23009800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>7837100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>14807600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>11388300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>14584600</v>
       </c>
     </row>
